--- a/datasets/Data_training/AQI_daily_2024_IGI_Airport_(T3)_Delhi_IMD_2024.xlsx
+++ b/datasets/Data_training/AQI_daily_2024_IGI_Airport_(T3)_Delhi_IMD_2024.xlsx
@@ -1,24 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Navyaa\college\ecoaware\datasets\Data_training\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE46CD4E-FCDD-440E-80E4-DE0099C6190A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
-    <t>Day</t>
-  </si>
-  <si>
     <t>January</t>
   </si>
   <si>
@@ -80,13 +83,16 @@
   </si>
   <si>
     <t>% of Availability</t>
+  </si>
+  <si>
+    <t>Date</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,13 +155,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -193,7 +207,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -227,6 +241,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -261,9 +276,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -436,52 +452,52 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -516,7 +532,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -545,7 +561,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -580,7 +596,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -621,7 +637,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -653,7 +669,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -685,7 +701,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -720,7 +736,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -752,7 +768,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -787,7 +803,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -822,7 +838,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -851,7 +867,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -883,7 +899,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -918,7 +934,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -947,7 +963,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -985,7 +1001,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1017,7 +1033,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1049,7 +1065,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1084,7 +1100,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1116,7 +1132,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1151,7 +1167,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1183,7 +1199,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1218,7 +1234,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1250,7 +1266,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1291,7 +1307,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1326,7 +1342,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1367,7 +1383,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1405,7 +1421,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1443,7 +1459,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1481,7 +1497,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1516,7 +1532,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1539,14 +1555,14 @@
         <v>340</v>
       </c>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
-      <c r="A34" t="s">
-        <v>14</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -1561,9 +1577,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D35">
         <v>2</v>
@@ -1590,9 +1606,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C36">
         <v>16</v>
@@ -1625,9 +1641,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B37">
         <v>4</v>
@@ -1660,9 +1676,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B38">
         <v>19</v>
@@ -1680,9 +1696,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B39">
         <v>3</v>
@@ -1694,7 +1710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B40">
         <v>5</v>
       </c>
@@ -1732,14 +1748,14 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13">
-      <c r="A42" t="s">
-        <v>21</v>
       </c>
       <c r="B42">
         <v>83</v>
